--- a/artfynd/A 43740-2021 artfynd.xlsx
+++ b/artfynd/A 43740-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43740-2021 artfynd.xlsx
+++ b/artfynd/A 43740-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1937882</v>
+        <v>113887987</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6800 m SSV om Rusele, Ly lm</t>
+          <t>Rusele, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>643099.7877162201</v>
+        <v>643380</v>
       </c>
       <c r="R2" t="n">
-        <v>7202477.263639273</v>
+        <v>7202550</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-07-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +784,7 @@
         <v>1937881</v>
       </c>
       <c r="B3" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>643167.1333280741</v>
+        <v>643167</v>
       </c>
       <c r="R3" t="n">
-        <v>7202386.130496575</v>
+        <v>7202386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +849,9 @@
           <t>2009-07-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +866,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1937883</v>
+        <v>1937882</v>
       </c>
       <c r="B4" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,14 +909,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6600 m SSV om Rusele, Ly lm</t>
+          <t>6800 m SSV om Rusele, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>643601.0465531606</v>
+        <v>643100</v>
       </c>
       <c r="R4" t="n">
-        <v>7202380.592038833</v>
+        <v>7202477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +946,9 @@
           <t>2009-07-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-07-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,62 +963,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96484912</v>
+        <v>1937883</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mittisundsmarken, Lycksele, Ly lm</t>
+          <t>6600 m SSV om Rusele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>643585.8193778318</v>
+        <v>643601</v>
       </c>
       <c r="R5" t="n">
-        <v>7202387.511438184</v>
+        <v>7202381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1040,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Via Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>96484913</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>643585.778635897</v>
+        <v>643586</v>
       </c>
       <c r="R6" t="n">
-        <v>7202388.359579807</v>
+        <v>7202388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,19 +1140,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,15 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113886841</v>
+        <v>113886750</v>
       </c>
       <c r="B7" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>643585</v>
+        <v>643531</v>
       </c>
       <c r="R7" t="n">
-        <v>7202384</v>
+        <v>7202410</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,15 +1279,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113887832</v>
+        <v>113886757</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,21 +1290,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1398,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>643674</v>
+        <v>643548</v>
       </c>
       <c r="R8" t="n">
-        <v>7202300</v>
+        <v>7202445</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,15 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113886750</v>
+        <v>113886840</v>
       </c>
       <c r="B9" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>643531</v>
+        <v>643181</v>
       </c>
       <c r="R9" t="n">
-        <v>7202410</v>
+        <v>7202521</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113886870</v>
+        <v>113886841</v>
       </c>
       <c r="B10" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>643522</v>
+        <v>643585</v>
       </c>
       <c r="R10" t="n">
-        <v>7202439</v>
+        <v>7202384</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,15 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113887987</v>
+        <v>113886870</v>
       </c>
       <c r="B11" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1731,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>643380</v>
+        <v>643522</v>
       </c>
       <c r="R11" t="n">
-        <v>7202550</v>
+        <v>7202439</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1798,57 +1703,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113886757</v>
+        <v>96484912</v>
       </c>
       <c r="B12" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rusele, Ly lm</t>
+          <t>Mittisundsmarken, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>643548</v>
+        <v>643586</v>
       </c>
       <c r="R12" t="n">
-        <v>7202445</v>
+        <v>7202387</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,17 +1768,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,49 +1788,48 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113886840</v>
+        <v>113887832</v>
       </c>
       <c r="B13" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1953,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>643181</v>
+        <v>643674</v>
       </c>
       <c r="R13" t="n">
-        <v>7202521</v>
+        <v>7202300</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 43740-2021 artfynd.xlsx
+++ b/artfynd/A 43740-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887832</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937882</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937883</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484913</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886750</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886757</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886840</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886841</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886870</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,8 +1967,27 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484912</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>